--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1655,6 +1655,969 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120396577</v>
+      </c>
+      <c r="B10" t="n">
+        <v>94701</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>535</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dicranodontium denudatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>325846</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6434968</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Brant</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120396572</v>
+      </c>
+      <c r="B11" t="n">
+        <v>74640</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>306</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>326009</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6435073</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skada på gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120396574</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96580</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2609</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsfliksmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lejeunea cavifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>325909</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6434968</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fin, lite grövre ek</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120396579</v>
+      </c>
+      <c r="B13" t="n">
+        <v>74646</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>308</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>325957</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6434924</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Högstubbe gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120396586</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96558</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>326198</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6434674</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Slänt till kulle</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120396578</v>
+      </c>
+      <c r="B15" t="n">
+        <v>94701</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>535</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dicranodontium denudatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>325834</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6434949</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120396573</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96198</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>325945</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6434987</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Vid samling av döda täd</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120396581</v>
+      </c>
+      <c r="B17" t="n">
+        <v>74646</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>308</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>326389</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6434623</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Död tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120396575</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74646</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>308</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>325880</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6435003</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Torraka i brant</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120396577</v>
+        <v>120396581</v>
       </c>
       <c r="B10" t="n">
-        <v>94701</v>
+        <v>74646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,25 +1669,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>535</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325846</v>
+        <v>326389</v>
       </c>
       <c r="R10" t="n">
-        <v>6434968</v>
+        <v>6434623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Brant</t>
+          <t>Död tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120396572</v>
+        <v>120396578</v>
       </c>
       <c r="B11" t="n">
-        <v>74640</v>
+        <v>94701</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>306</v>
+        <v>535</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>326009</v>
+        <v>325834</v>
       </c>
       <c r="R11" t="n">
-        <v>6435073</v>
+        <v>6434949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Skada på gran</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120396574</v>
+        <v>120396573</v>
       </c>
       <c r="B12" t="n">
-        <v>96580</v>
+        <v>96198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,21 +1887,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2609</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325909</v>
+        <v>325945</v>
       </c>
       <c r="R12" t="n">
-        <v>6434968</v>
+        <v>6434987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fin, lite grövre ek</t>
+          <t>Vid samling av döda täd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,7 +1978,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120396579</v>
+        <v>120396575</v>
       </c>
       <c r="B13" t="n">
         <v>74646</v>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325957</v>
+        <v>325880</v>
       </c>
       <c r="R13" t="n">
-        <v>6434924</v>
+        <v>6435003</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Högstubbe gran</t>
+          <t>Torraka i brant</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120396586</v>
+        <v>120396574</v>
       </c>
       <c r="B14" t="n">
-        <v>96558</v>
+        <v>96580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2606</v>
+        <v>2609</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>326198</v>
+        <v>325909</v>
       </c>
       <c r="R14" t="n">
-        <v>6434674</v>
+        <v>6434968</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Slänt till kulle</t>
+          <t>Fin, lite grövre ek</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120396578</v>
+        <v>120396579</v>
       </c>
       <c r="B15" t="n">
-        <v>94701</v>
+        <v>74646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,25 +2204,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>535</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325834</v>
+        <v>325957</v>
       </c>
       <c r="R15" t="n">
-        <v>6434949</v>
+        <v>6434924</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Högstubbe gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120396573</v>
+        <v>120396586</v>
       </c>
       <c r="B16" t="n">
-        <v>96198</v>
+        <v>96558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325945</v>
+        <v>326198</v>
       </c>
       <c r="R16" t="n">
-        <v>6434987</v>
+        <v>6434674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Vid samling av döda täd</t>
+          <t>Slänt till kulle</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120396581</v>
+        <v>120396577</v>
       </c>
       <c r="B17" t="n">
-        <v>74646</v>
+        <v>94701</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,25 +2418,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>535</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>326389</v>
+        <v>325846</v>
       </c>
       <c r="R17" t="n">
-        <v>6434623</v>
+        <v>6434968</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Död tall</t>
+          <t>Brant</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120396575</v>
+        <v>120396572</v>
       </c>
       <c r="B18" t="n">
-        <v>74646</v>
+        <v>74640</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325880</v>
+        <v>326009</v>
       </c>
       <c r="R18" t="n">
-        <v>6435003</v>
+        <v>6435073</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Torraka i brant</t>
+          <t>Skada på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,6 +2617,2317 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120482265</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>325912</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6434966</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120482273</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>325883</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6434952</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120482269</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>325947</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6434931</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120482301</v>
+      </c>
+      <c r="B22" t="n">
+        <v>84451</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>241</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>325958</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6434984</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120482255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>325854</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6434976</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120482275</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58176</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>325846</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6434961</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120482299</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96558</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>325843</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6434980</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120482259</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>325874</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6435000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120482257</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>325867</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6434934</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120482562</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80802</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3929</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Läderskål</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Encoelia furfuracea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Roth.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>326094</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6434725</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120482292</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80499</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>326154</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6435071</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120482283</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96198</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>326161</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6435085</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120482287</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80499</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>325854</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6434976</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120482263</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>325867</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6434934</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120482289</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80499</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>325874</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6435000</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120482285</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>326004</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6434838</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120482300</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90594</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>325883</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6434933</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Äldre granlåga.</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120482298</v>
+      </c>
+      <c r="B36" t="n">
+        <v>96558</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>325835</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6434955</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120482306</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>325833</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6434958</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120482281</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>325953</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6434938</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120396581</v>
+        <v>120482281</v>
       </c>
       <c r="B10" t="n">
-        <v>74646</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,34 +1673,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>326389</v>
+        <v>325953</v>
       </c>
       <c r="R10" t="n">
-        <v>6434623</v>
+        <v>6434938</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,11 +1747,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Död tall</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1752,22 +1759,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120396578</v>
+        <v>120482275</v>
       </c>
       <c r="B11" t="n">
-        <v>94701</v>
+        <v>58176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,34 +1787,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>535</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325834</v>
+        <v>325846</v>
       </c>
       <c r="R11" t="n">
-        <v>6434949</v>
+        <v>6434961</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,11 +1849,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1859,22 +1861,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120396573</v>
+        <v>120482255</v>
       </c>
       <c r="B12" t="n">
-        <v>96198</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,38 +1885,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325945</v>
+        <v>325854</v>
       </c>
       <c r="R12" t="n">
-        <v>6434987</v>
+        <v>6434976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,11 +1963,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Vid samling av döda täd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1966,22 +1975,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120396575</v>
+        <v>120482289</v>
       </c>
       <c r="B13" t="n">
-        <v>74646</v>
+        <v>80499</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,34 +2003,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325880</v>
+        <v>325874</v>
       </c>
       <c r="R13" t="n">
-        <v>6435003</v>
+        <v>6435000</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,11 +2065,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Torraka i brant</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2069,26 +2073,41 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120396574</v>
+        <v>120482259</v>
       </c>
       <c r="B14" t="n">
-        <v>96580</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,38 +2116,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2609</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325909</v>
+        <v>325874</v>
       </c>
       <c r="R14" t="n">
-        <v>6434968</v>
+        <v>6435000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,11 +2190,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fin, lite grövre ek</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2180,22 +2202,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120396579</v>
+        <v>120482298</v>
       </c>
       <c r="B15" t="n">
-        <v>74646</v>
+        <v>96558</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,38 +2226,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>2606</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325957</v>
+        <v>325835</v>
       </c>
       <c r="R15" t="n">
-        <v>6434924</v>
+        <v>6434955</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,39 +2296,50 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Högstubbe gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120396586</v>
+        <v>120482265</v>
       </c>
       <c r="B16" t="n">
-        <v>96558</v>
+        <v>5189</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,34 +2352,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>326198</v>
+        <v>325912</v>
       </c>
       <c r="R16" t="n">
-        <v>6434674</v>
+        <v>6434966</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,11 +2414,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Slänt till kulle</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2390,26 +2422,41 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120396577</v>
+        <v>120482301</v>
       </c>
       <c r="B17" t="n">
-        <v>94701</v>
+        <v>84451</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,38 +2465,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>535</v>
+        <v>241</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325846</v>
+        <v>325958</v>
       </c>
       <c r="R17" t="n">
-        <v>6434968</v>
+        <v>6434984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,39 +2534,55 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Brant</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120396572</v>
+        <v>120482257</v>
       </c>
       <c r="B18" t="n">
-        <v>74640</v>
+        <v>5169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,34 +2595,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>306</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>326009</v>
+        <v>325867</v>
       </c>
       <c r="R18" t="n">
-        <v>6435073</v>
+        <v>6434934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,11 +2657,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Skada på gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2604,26 +2665,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120482265</v>
+        <v>120482292</v>
       </c>
       <c r="B19" t="n">
-        <v>5189</v>
+        <v>80499</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,25 +2708,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2660,10 +2736,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>325912</v>
+        <v>326154</v>
       </c>
       <c r="R19" t="n">
-        <v>6434966</v>
+        <v>6435071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,10 +2813,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120482273</v>
+        <v>120482283</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2749,50 +2825,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>325883</v>
+        <v>326161</v>
       </c>
       <c r="R20" t="n">
-        <v>6434952</v>
+        <v>6435085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2851,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120482269</v>
+        <v>120482299</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
+        <v>96558</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,34 +2931,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325947</v>
+        <v>325843</v>
       </c>
       <c r="R21" t="n">
-        <v>6434931</v>
+        <v>6434980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,22 +3003,23 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2968,10 +3037,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120482301</v>
+        <v>120482273</v>
       </c>
       <c r="B22" t="n">
-        <v>84451</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,26 +3053,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>241</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3011,10 +3089,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325958</v>
+        <v>325883</v>
       </c>
       <c r="R22" t="n">
-        <v>6434984</v>
+        <v>6434952</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3055,29 +3133,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3094,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120482255</v>
+        <v>120482306</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>91200</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,50 +3163,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>325854</v>
+        <v>325833</v>
       </c>
       <c r="R23" t="n">
-        <v>6434976</v>
+        <v>6434958</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3192,6 +3237,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3208,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120482275</v>
+        <v>120482263</v>
       </c>
       <c r="B24" t="n">
-        <v>58176</v>
+        <v>5189</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,21 +3284,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208249</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3248,10 +3308,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>325846</v>
+        <v>325867</v>
       </c>
       <c r="R24" t="n">
-        <v>6434961</v>
+        <v>6434934</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3294,6 +3354,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3310,10 +3385,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120482299</v>
+        <v>120482285</v>
       </c>
       <c r="B25" t="n">
-        <v>96558</v>
+        <v>96885</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,38 +3401,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2606</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>325843</v>
+        <v>326004</v>
       </c>
       <c r="R25" t="n">
-        <v>6434980</v>
+        <v>6434838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3398,24 +3469,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3432,10 +3487,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120482259</v>
+        <v>120482562</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>80802</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,35 +3499,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>3929</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3480,13 +3530,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>325874</v>
+        <v>326094</v>
       </c>
       <c r="R26" t="n">
-        <v>6435000</v>
+        <v>6434725</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3524,8 +3574,24 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3542,10 +3608,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120482257</v>
+        <v>120482269</v>
       </c>
       <c r="B27" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3558,21 +3624,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3582,10 +3648,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>325867</v>
+        <v>325947</v>
       </c>
       <c r="R27" t="n">
-        <v>6434934</v>
+        <v>6434931</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3659,10 +3725,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120482562</v>
+        <v>120482300</v>
       </c>
       <c r="B28" t="n">
-        <v>80802</v>
+        <v>90594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3671,25 +3737,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3929</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3702,13 +3768,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>326094</v>
+        <v>325883</v>
       </c>
       <c r="R28" t="n">
-        <v>6434725</v>
+        <v>6434933</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,17 +3818,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>hassel</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Äldre granlåga.</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Picea abies # Äldre granlåga.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3780,7 +3851,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120482292</v>
+        <v>120482287</v>
       </c>
       <c r="B29" t="n">
         <v>80499</v>
@@ -3820,10 +3891,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>326154</v>
+        <v>325854</v>
       </c>
       <c r="R29" t="n">
-        <v>6435071</v>
+        <v>6434976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3897,10 +3968,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120482283</v>
+        <v>120396574</v>
       </c>
       <c r="B30" t="n">
-        <v>96198</v>
+        <v>96580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,34 +3984,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2569</v>
+        <v>2609</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>326161</v>
+        <v>325909</v>
       </c>
       <c r="R30" t="n">
-        <v>6435085</v>
+        <v>6434968</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,6 +4046,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Fin, lite grövre ek</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3987,22 +4063,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120482287</v>
+        <v>120396575</v>
       </c>
       <c r="B31" t="n">
-        <v>80499</v>
+        <v>74646</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4015,34 +4095,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>325854</v>
+        <v>325880</v>
       </c>
       <c r="R31" t="n">
-        <v>6434976</v>
+        <v>6435003</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4077,6 +4157,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Torraka i brant</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4085,41 +4170,30 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120482263</v>
+        <v>120396581</v>
       </c>
       <c r="B32" t="n">
-        <v>5189</v>
+        <v>74646</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4128,38 +4202,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>325867</v>
+        <v>326389</v>
       </c>
       <c r="R32" t="n">
-        <v>6434934</v>
+        <v>6434623</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4194,6 +4268,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Död tall</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4202,41 +4281,30 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120482289</v>
+        <v>120396573</v>
       </c>
       <c r="B33" t="n">
-        <v>80499</v>
+        <v>96198</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4245,38 +4313,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>325874</v>
+        <v>325945</v>
       </c>
       <c r="R33" t="n">
-        <v>6435000</v>
+        <v>6434987</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4311,6 +4379,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Vid samling av döda täd</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4319,41 +4392,30 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120482285</v>
+        <v>120396578</v>
       </c>
       <c r="B34" t="n">
-        <v>96885</v>
+        <v>94701</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4366,34 +4428,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>535</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>326004</v>
+        <v>325834</v>
       </c>
       <c r="R34" t="n">
-        <v>6434838</v>
+        <v>6434949</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4428,6 +4490,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4440,22 +4507,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120482300</v>
+        <v>120396572</v>
       </c>
       <c r="B35" t="n">
-        <v>90594</v>
+        <v>74640</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4464,41 +4535,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>325883</v>
+        <v>326009</v>
       </c>
       <c r="R35" t="n">
-        <v>6434933</v>
+        <v>6435073</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4533,55 +4601,43 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Skada på gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Äldre granlåga.</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120482298</v>
+        <v>120396579</v>
       </c>
       <c r="B36" t="n">
-        <v>96558</v>
+        <v>74646</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4590,42 +4646,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>325835</v>
+        <v>325957</v>
       </c>
       <c r="R36" t="n">
-        <v>6434955</v>
+        <v>6434924</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4660,50 +4712,43 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Högstubbe gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120482306</v>
+        <v>120396577</v>
       </c>
       <c r="B37" t="n">
-        <v>91200</v>
+        <v>94701</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4716,34 +4761,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1339</v>
+        <v>535</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>325833</v>
+        <v>325846</v>
       </c>
       <c r="R37" t="n">
-        <v>6434958</v>
+        <v>6434968</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4778,6 +4823,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Brant</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4786,41 +4836,30 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120482281</v>
+        <v>120396586</v>
       </c>
       <c r="B38" t="n">
-        <v>57473</v>
+        <v>96558</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4829,50 +4868,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>2606</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>325953</v>
+        <v>326198</v>
       </c>
       <c r="R38" t="n">
-        <v>6434938</v>
+        <v>6434674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4907,6 +4934,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Slänt till kulle</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4919,15 +4951,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4965,6 +4965,226 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120516637</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>325879</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6434967</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120516634</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>326160</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6435095</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120482281</v>
+        <v>120482275</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>58176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,50 +1669,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325953</v>
+        <v>325846</v>
       </c>
       <c r="R10" t="n">
-        <v>6434938</v>
+        <v>6434961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1771,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120482275</v>
+        <v>120482269</v>
       </c>
       <c r="B11" t="n">
-        <v>58176</v>
+        <v>5189</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1787,21 +1775,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1811,10 +1799,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325846</v>
+        <v>325947</v>
       </c>
       <c r="R11" t="n">
-        <v>6434961</v>
+        <v>6434931</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1857,6 +1845,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1873,10 +1876,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120482255</v>
+        <v>120482300</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>90594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,35 +1892,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1925,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325854</v>
+        <v>325883</v>
       </c>
       <c r="R12" t="n">
-        <v>6434976</v>
+        <v>6434933</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1969,8 +1963,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Äldre granlåga.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1987,10 +2002,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120482289</v>
+        <v>120482257</v>
       </c>
       <c r="B13" t="n">
-        <v>80499</v>
+        <v>5169</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,25 +2014,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2027,10 +2042,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325874</v>
+        <v>325867</v>
       </c>
       <c r="R13" t="n">
-        <v>6435000</v>
+        <v>6434934</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2104,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120482259</v>
+        <v>120482283</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2116,46 +2131,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325874</v>
+        <v>326161</v>
       </c>
       <c r="R14" t="n">
-        <v>6435000</v>
+        <v>6435085</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2214,10 +2221,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120482298</v>
+        <v>120482263</v>
       </c>
       <c r="B15" t="n">
-        <v>96558</v>
+        <v>5189</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,38 +2237,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325835</v>
+        <v>325867</v>
       </c>
       <c r="R15" t="n">
-        <v>6434955</v>
+        <v>6434934</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,23 +2305,22 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2336,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120482265</v>
+        <v>120482299</v>
       </c>
       <c r="B16" t="n">
-        <v>5189</v>
+        <v>96558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2352,34 +2354,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325912</v>
+        <v>325843</v>
       </c>
       <c r="R16" t="n">
-        <v>6434966</v>
+        <v>6434980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2420,22 +2426,23 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2453,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120482301</v>
+        <v>120482562</v>
       </c>
       <c r="B17" t="n">
-        <v>84451</v>
+        <v>80802</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2465,25 +2472,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>241</v>
+        <v>3929</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2496,13 +2503,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325958</v>
+        <v>326094</v>
       </c>
       <c r="R17" t="n">
-        <v>6434984</v>
+        <v>6434725</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2546,22 +2553,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>hassel</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Corylus avellana</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2579,10 +2581,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120482257</v>
+        <v>120482298</v>
       </c>
       <c r="B18" t="n">
-        <v>5169</v>
+        <v>96558</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,34 +2597,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325867</v>
+        <v>325835</v>
       </c>
       <c r="R18" t="n">
-        <v>6434934</v>
+        <v>6434955</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2663,22 +2669,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2813,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120482283</v>
+        <v>120482265</v>
       </c>
       <c r="B20" t="n">
-        <v>96198</v>
+        <v>5189</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2829,21 +2836,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2853,10 +2860,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>326161</v>
+        <v>325912</v>
       </c>
       <c r="R20" t="n">
-        <v>6435085</v>
+        <v>6434966</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2899,6 +2906,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2915,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120482299</v>
+        <v>120482289</v>
       </c>
       <c r="B21" t="n">
-        <v>96558</v>
+        <v>80499</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2927,42 +2949,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325843</v>
+        <v>325874</v>
       </c>
       <c r="R21" t="n">
-        <v>6434980</v>
+        <v>6435000</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,23 +3021,22 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3037,10 +3054,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120482273</v>
+        <v>120482301</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>84451</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3053,35 +3070,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>241</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3089,10 +3097,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325883</v>
+        <v>325958</v>
       </c>
       <c r="R22" t="n">
-        <v>6434952</v>
+        <v>6434984</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3133,8 +3141,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3151,10 +3180,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120482306</v>
+        <v>120482273</v>
       </c>
       <c r="B23" t="n">
-        <v>91200</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3163,38 +3192,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>325833</v>
+        <v>325883</v>
       </c>
       <c r="R23" t="n">
-        <v>6434958</v>
+        <v>6434952</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3237,21 +3278,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3268,10 +3294,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120482263</v>
+        <v>120482259</v>
       </c>
       <c r="B24" t="n">
-        <v>5189</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3280,20 +3306,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3302,16 +3328,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>325867</v>
+        <v>325874</v>
       </c>
       <c r="R24" t="n">
-        <v>6434934</v>
+        <v>6435000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3354,21 +3388,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3385,10 +3404,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120482285</v>
+        <v>120482306</v>
       </c>
       <c r="B25" t="n">
-        <v>96885</v>
+        <v>91200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,21 +3420,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>1339</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3425,10 +3444,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>326004</v>
+        <v>325833</v>
       </c>
       <c r="R25" t="n">
-        <v>6434838</v>
+        <v>6434958</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,6 +3490,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3487,10 +3521,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120482562</v>
+        <v>120482287</v>
       </c>
       <c r="B26" t="n">
-        <v>80802</v>
+        <v>80499</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3499,44 +3533,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3929</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>326094</v>
+        <v>325854</v>
       </c>
       <c r="R26" t="n">
-        <v>6434725</v>
+        <v>6434976</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3574,23 +3605,22 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>hassel</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Corylus avellana</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3608,10 +3638,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120482269</v>
+        <v>120482255</v>
       </c>
       <c r="B27" t="n">
-        <v>5189</v>
+        <v>57473</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3620,38 +3650,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>325947</v>
+        <v>325854</v>
       </c>
       <c r="R27" t="n">
-        <v>6434931</v>
+        <v>6434976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3694,21 +3736,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3725,10 +3752,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120482300</v>
+        <v>120482281</v>
       </c>
       <c r="B28" t="n">
-        <v>90594</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3741,26 +3768,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3768,10 +3804,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>325883</v>
+        <v>325953</v>
       </c>
       <c r="R28" t="n">
-        <v>6434933</v>
+        <v>6434938</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3812,29 +3848,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Äldre granlåga.</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3851,10 +3866,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120482287</v>
+        <v>120482285</v>
       </c>
       <c r="B29" t="n">
-        <v>80499</v>
+        <v>96885</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3863,25 +3878,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3891,10 +3906,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>325854</v>
+        <v>326004</v>
       </c>
       <c r="R29" t="n">
-        <v>6434976</v>
+        <v>6434838</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3937,21 +3952,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3968,10 +3968,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120396574</v>
+        <v>120396581</v>
       </c>
       <c r="B30" t="n">
-        <v>96580</v>
+        <v>74646</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3980,25 +3980,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2609</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>325909</v>
+        <v>326389</v>
       </c>
       <c r="R30" t="n">
-        <v>6434968</v>
+        <v>6434623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Fin, lite grövre ek</t>
+          <t>Död tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4073,16 +4073,16 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120396575</v>
+        <v>120396586</v>
       </c>
       <c r="B31" t="n">
-        <v>74646</v>
+        <v>96558</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4091,25 +4091,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>325880</v>
+        <v>326198</v>
       </c>
       <c r="R31" t="n">
-        <v>6435003</v>
+        <v>6434674</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Torraka i brant</t>
+          <t>Slänt till kulle</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4184,13 +4184,13 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120396581</v>
+        <v>120396575</v>
       </c>
       <c r="B32" t="n">
         <v>74646</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>326389</v>
+        <v>325880</v>
       </c>
       <c r="R32" t="n">
-        <v>6434623</v>
+        <v>6435003</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Död tall</t>
+          <t>Torraka i brant</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
@@ -4517,16 +4517,16 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120396572</v>
+        <v>120396579</v>
       </c>
       <c r="B35" t="n">
-        <v>74640</v>
+        <v>74646</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4535,25 +4535,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>326009</v>
+        <v>325957</v>
       </c>
       <c r="R35" t="n">
-        <v>6435073</v>
+        <v>6434924</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Skada på gran</t>
+          <t>Högstubbe gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4628,16 +4628,16 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120396579</v>
+        <v>120396572</v>
       </c>
       <c r="B36" t="n">
-        <v>74646</v>
+        <v>74640</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4646,25 +4646,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>325957</v>
+        <v>326009</v>
       </c>
       <c r="R36" t="n">
-        <v>6434924</v>
+        <v>6435073</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Högstubbe gran</t>
+          <t>Skada på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4739,16 +4739,16 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120396577</v>
+        <v>120516637</v>
       </c>
       <c r="B37" t="n">
-        <v>94701</v>
+        <v>57336</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4757,41 +4757,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>535</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>325846</v>
+        <v>325879</v>
       </c>
       <c r="R37" t="n">
-        <v>6434968</v>
+        <v>6434967</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4821,11 +4829,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Brant</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4840,26 +4843,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120396586</v>
+        <v>120516634</v>
       </c>
       <c r="B38" t="n">
-        <v>96558</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4868,41 +4867,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>326198</v>
+        <v>326160</v>
       </c>
       <c r="R38" t="n">
-        <v>6434674</v>
+        <v>6435095</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4932,11 +4939,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Slänt till kulle</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4951,77 +4953,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120516637</v>
+        <v>120396574</v>
       </c>
       <c r="B39" t="n">
-        <v>57336</v>
+        <v>96580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>2609</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>325879</v>
+        <v>325909</v>
       </c>
       <c r="R39" t="n">
-        <v>6434967</v>
+        <v>6434968</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5051,6 +5041,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Fin, lite grövre ek</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5065,73 +5060,69 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120516634</v>
+        <v>120396577</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>94701</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>535</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>326160</v>
+        <v>325846</v>
       </c>
       <c r="R40" t="n">
-        <v>6435095</v>
+        <v>6434968</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5161,6 +5152,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Brant</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5175,15 +5171,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120482275</v>
+        <v>120482300</v>
       </c>
       <c r="B10" t="n">
-        <v>58176</v>
+        <v>90594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,38 +1669,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325846</v>
+        <v>325883</v>
       </c>
       <c r="R10" t="n">
-        <v>6434961</v>
+        <v>6434933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,8 +1744,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Äldre granlåga.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1759,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120482269</v>
+        <v>120482281</v>
       </c>
       <c r="B11" t="n">
-        <v>5189</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,38 +1795,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325947</v>
+        <v>325953</v>
       </c>
       <c r="R11" t="n">
-        <v>6434931</v>
+        <v>6434938</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,21 +1881,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1876,10 +1897,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120482300</v>
+        <v>120482255</v>
       </c>
       <c r="B12" t="n">
-        <v>90594</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,26 +1913,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1919,10 +1949,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325883</v>
+        <v>325854</v>
       </c>
       <c r="R12" t="n">
-        <v>6434933</v>
+        <v>6434976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1963,29 +1993,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Äldre granlåga.</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2002,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120482257</v>
+        <v>120482299</v>
       </c>
       <c r="B13" t="n">
-        <v>5169</v>
+        <v>96558</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2018,34 +2027,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325867</v>
+        <v>325843</v>
       </c>
       <c r="R13" t="n">
-        <v>6434934</v>
+        <v>6434980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,22 +2099,23 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2119,10 +2133,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120482283</v>
+        <v>120482289</v>
       </c>
       <c r="B14" t="n">
-        <v>96198</v>
+        <v>80499</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,25 +2145,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2159,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>326161</v>
+        <v>325874</v>
       </c>
       <c r="R14" t="n">
-        <v>6435085</v>
+        <v>6435000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2205,6 +2219,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2221,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120482263</v>
+        <v>120482257</v>
       </c>
       <c r="B15" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,21 +2266,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2338,10 +2367,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120482299</v>
+        <v>120482285</v>
       </c>
       <c r="B16" t="n">
-        <v>96558</v>
+        <v>96885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,38 +2383,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325843</v>
+        <v>326004</v>
       </c>
       <c r="R16" t="n">
-        <v>6434980</v>
+        <v>6434838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2426,24 +2451,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2460,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120482562</v>
+        <v>120482273</v>
       </c>
       <c r="B17" t="n">
-        <v>80802</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,30 +2481,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3929</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2503,13 +2521,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>326094</v>
+        <v>325883</v>
       </c>
       <c r="R17" t="n">
-        <v>6434725</v>
+        <v>6434952</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2547,24 +2565,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2581,10 +2583,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120482298</v>
+        <v>120482287</v>
       </c>
       <c r="B18" t="n">
-        <v>96558</v>
+        <v>80499</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2593,42 +2595,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2606</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325835</v>
+        <v>325854</v>
       </c>
       <c r="R18" t="n">
-        <v>6434955</v>
+        <v>6434976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2669,23 +2667,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2703,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120482292</v>
+        <v>120482298</v>
       </c>
       <c r="B19" t="n">
-        <v>80499</v>
+        <v>96558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,38 +2712,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>326154</v>
+        <v>325835</v>
       </c>
       <c r="R19" t="n">
-        <v>6435071</v>
+        <v>6434955</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2787,22 +2788,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2820,7 +2822,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120482265</v>
+        <v>120482269</v>
       </c>
       <c r="B20" t="n">
         <v>5189</v>
@@ -2860,10 +2862,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>325912</v>
+        <v>325947</v>
       </c>
       <c r="R20" t="n">
-        <v>6434966</v>
+        <v>6434931</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,10 +2939,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120482289</v>
+        <v>120482275</v>
       </c>
       <c r="B21" t="n">
-        <v>80499</v>
+        <v>58176</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,25 +2951,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>208249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2977,10 +2979,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325874</v>
+        <v>325846</v>
       </c>
       <c r="R21" t="n">
-        <v>6435000</v>
+        <v>6434961</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3023,21 +3025,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3054,10 +3041,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120482301</v>
+        <v>120482263</v>
       </c>
       <c r="B22" t="n">
-        <v>84451</v>
+        <v>5189</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3066,41 +3053,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>241</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325958</v>
+        <v>325867</v>
       </c>
       <c r="R22" t="n">
-        <v>6434984</v>
+        <v>6434934</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3141,7 +3125,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3155,14 +3138,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3180,10 +3158,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120482273</v>
+        <v>120482562</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>80802</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3192,39 +3170,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>3929</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Roth.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3232,13 +3201,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>325883</v>
+        <v>326094</v>
       </c>
       <c r="R23" t="n">
-        <v>6434952</v>
+        <v>6434725</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3276,8 +3245,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3521,10 +3506,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120482287</v>
+        <v>120482265</v>
       </c>
       <c r="B26" t="n">
-        <v>80499</v>
+        <v>5189</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3533,25 +3518,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3561,10 +3546,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>325854</v>
+        <v>325912</v>
       </c>
       <c r="R26" t="n">
-        <v>6434976</v>
+        <v>6434966</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3638,10 +3623,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120482255</v>
+        <v>120482301</v>
       </c>
       <c r="B27" t="n">
-        <v>57473</v>
+        <v>84451</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3654,35 +3639,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>241</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3690,10 +3666,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>325854</v>
+        <v>325958</v>
       </c>
       <c r="R27" t="n">
-        <v>6434976</v>
+        <v>6434984</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3734,8 +3710,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3752,10 +3749,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120482281</v>
+        <v>120482292</v>
       </c>
       <c r="B28" t="n">
-        <v>57473</v>
+        <v>80499</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3768,46 +3765,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>325953</v>
+        <v>326154</v>
       </c>
       <c r="R28" t="n">
-        <v>6434938</v>
+        <v>6435071</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3850,6 +3835,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3866,10 +3866,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120482285</v>
+        <v>120482283</v>
       </c>
       <c r="B29" t="n">
-        <v>96885</v>
+        <v>96198</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3882,21 +3882,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>326004</v>
+        <v>326161</v>
       </c>
       <c r="R29" t="n">
-        <v>6434838</v>
+        <v>6435085</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3968,10 +3968,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120396581</v>
+        <v>120396572</v>
       </c>
       <c r="B30" t="n">
-        <v>74646</v>
+        <v>74640</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3980,25 +3980,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>326389</v>
+        <v>326009</v>
       </c>
       <c r="R30" t="n">
-        <v>6434623</v>
+        <v>6435073</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Död tall</t>
+          <t>Skada på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4190,7 +4190,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120396575</v>
+        <v>120396579</v>
       </c>
       <c r="B32" t="n">
         <v>74646</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>325880</v>
+        <v>325957</v>
       </c>
       <c r="R32" t="n">
-        <v>6435003</v>
+        <v>6434924</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Torraka i brant</t>
+          <t>Högstubbe gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4301,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120396573</v>
+        <v>120396581</v>
       </c>
       <c r="B33" t="n">
-        <v>96198</v>
+        <v>74646</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4313,25 +4313,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>325945</v>
+        <v>326389</v>
       </c>
       <c r="R33" t="n">
-        <v>6434987</v>
+        <v>6434623</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Vid samling av döda täd</t>
+          <t>Död tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4412,10 +4412,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120396578</v>
+        <v>120396573</v>
       </c>
       <c r="B34" t="n">
-        <v>94701</v>
+        <v>96198</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4428,21 +4428,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>535</v>
+        <v>2569</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>325834</v>
+        <v>325945</v>
       </c>
       <c r="R34" t="n">
-        <v>6434949</v>
+        <v>6434987</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Vid samling av döda täd</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,7 +4523,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120396579</v>
+        <v>120396575</v>
       </c>
       <c r="B35" t="n">
         <v>74646</v>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>325957</v>
+        <v>325880</v>
       </c>
       <c r="R35" t="n">
-        <v>6434924</v>
+        <v>6435003</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Högstubbe gran</t>
+          <t>Torraka i brant</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120396572</v>
+        <v>120396578</v>
       </c>
       <c r="B36" t="n">
-        <v>74640</v>
+        <v>94701</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>306</v>
+        <v>535</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>326009</v>
+        <v>325834</v>
       </c>
       <c r="R36" t="n">
-        <v>6435073</v>
+        <v>6434949</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Skada på gran</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120482300</v>
+        <v>120482281</v>
       </c>
       <c r="B10" t="n">
-        <v>90594</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,26 +1673,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1700,10 +1709,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325883</v>
+        <v>325953</v>
       </c>
       <c r="R10" t="n">
-        <v>6434933</v>
+        <v>6434938</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1744,29 +1753,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Äldre granlåga.</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1783,10 +1771,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120482281</v>
+        <v>120482300</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>90594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1799,35 +1787,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1835,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325953</v>
+        <v>325883</v>
       </c>
       <c r="R11" t="n">
-        <v>6434938</v>
+        <v>6434933</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1879,8 +1858,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Äldre granlåga.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120482257</v>
+        <v>120482273</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2262,38 +2262,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325867</v>
+        <v>325883</v>
       </c>
       <c r="R15" t="n">
-        <v>6434934</v>
+        <v>6434952</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2336,21 +2348,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2367,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120482285</v>
+        <v>120482257</v>
       </c>
       <c r="B16" t="n">
-        <v>96885</v>
+        <v>5169</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2383,21 +2380,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2407,10 +2404,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>326004</v>
+        <v>325867</v>
       </c>
       <c r="R16" t="n">
-        <v>6434838</v>
+        <v>6434934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2453,6 +2450,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2469,10 +2481,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120482273</v>
+        <v>120482285</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,50 +2493,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325883</v>
+        <v>326004</v>
       </c>
       <c r="R17" t="n">
-        <v>6434952</v>
+        <v>6434838</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3158,10 +3158,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120482562</v>
+        <v>120482259</v>
       </c>
       <c r="B23" t="n">
-        <v>80802</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,30 +3170,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3929</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3201,13 +3206,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>326094</v>
+        <v>325874</v>
       </c>
       <c r="R23" t="n">
-        <v>6434725</v>
+        <v>6435000</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3245,24 +3250,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3279,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120482259</v>
+        <v>120482562</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>80802</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,35 +3280,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>3929</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3327,13 +3311,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>325874</v>
+        <v>326094</v>
       </c>
       <c r="R24" t="n">
-        <v>6435000</v>
+        <v>6434725</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3371,8 +3355,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3623,10 +3623,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120482301</v>
+        <v>120482283</v>
       </c>
       <c r="B27" t="n">
-        <v>84451</v>
+        <v>96198</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3635,41 +3635,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>241</v>
+        <v>2569</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>325958</v>
+        <v>326161</v>
       </c>
       <c r="R27" t="n">
-        <v>6434984</v>
+        <v>6435085</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3710,29 +3707,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3749,10 +3725,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120482292</v>
+        <v>120482301</v>
       </c>
       <c r="B28" t="n">
-        <v>80499</v>
+        <v>84451</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3765,34 +3741,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>241</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>326154</v>
+        <v>325958</v>
       </c>
       <c r="R28" t="n">
-        <v>6435071</v>
+        <v>6434984</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3833,6 +3812,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3846,9 +3826,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3866,10 +3851,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120482283</v>
+        <v>120482292</v>
       </c>
       <c r="B29" t="n">
-        <v>96198</v>
+        <v>80499</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3878,25 +3863,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3906,10 +3891,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>326161</v>
+        <v>326154</v>
       </c>
       <c r="R29" t="n">
-        <v>6435085</v>
+        <v>6435071</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3952,6 +3937,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,12 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>326023.3605734596</v>
+        <v>326023</v>
       </c>
       <c r="R7" t="n">
-        <v>6435018.306692057</v>
+        <v>6435018</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1361,19 +1356,9 @@
           <t>2001-10-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2001-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1403,7 +1388,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Gahnertz, Bertil Gilsenius</t>
+          <t>Bertil Gilsenius, Roger Gahnertz</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bertil Gilsenius, Roger Gahnertz</t>
+          <t>Roger Gahnertz, Bertil Gilsenius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97451</v>
+        <v>97457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>84693299</v>
       </c>
       <c r="B7" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4246503</v>
+        <v>4169272</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
+        <v>95510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1053843</v>
+        <v>4246503</v>
       </c>
       <c r="B3" t="n">
-        <v>83136</v>
+        <v>95521</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3518</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nornäbban, Svartedalen, Boh</t>
+          <t>300m NV om gården Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>326282.5541622447</v>
+        <v>326018.8867515359</v>
       </c>
       <c r="R3" t="n">
-        <v>6434686.656774394</v>
+        <v>6435013.198442956</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-10-25</t>
+          <t>2001-10-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-10-25</t>
+          <t>2001-10-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -891,33 +891,28 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Elaphomyces sp</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60197501</v>
+        <v>1053843</v>
       </c>
       <c r="B4" t="n">
-        <v>101222</v>
+        <v>83136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,52 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>837</v>
+        <v>3518</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypericum pulchrum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nornäbban, backe, Boh</t>
+          <t>Nornäbban, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>326084.2873558934</v>
+        <v>326282.5541622447</v>
       </c>
       <c r="R4" t="n">
-        <v>6434782.816282547</v>
+        <v>6434686.656774394</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +979,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-11</t>
+          <t>2011-10-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1005,7 +989,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-06-11</t>
+          <t>2011-10-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1021,23 +1005,33 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Elaphomyces sp</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karin Magnander</t>
+          <t>Johan Svedholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karin Magnander, Björn Dellming</t>
+          <t>Johan Svedholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60679007</v>
+        <v>60197501</v>
       </c>
       <c r="B5" t="n">
         <v>101222</v>
@@ -1072,29 +1066,29 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Billys backe, Nornäbban, Svartedalen (Kungälvs kommun), Boh</t>
+          <t>Nornäbban, backe, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>326062.0975395681</v>
+        <v>326084.2873558934</v>
       </c>
       <c r="R5" t="n">
-        <v>6434700.513468524</v>
+        <v>6434782.816282547</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1112,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-07-23</t>
+          <t>2016-06-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1128,7 +1122,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-07-23</t>
+          <t>2016-06-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1148,22 +1142,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Björn Dellming</t>
+          <t>Karin Magnander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Björn Dellming</t>
+          <t>Karin Magnander, Björn Dellming</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67640615</v>
+        <v>60679007</v>
       </c>
       <c r="B6" t="n">
-        <v>95717</v>
+        <v>101222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,52 +1166,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220686</v>
+        <v>837</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Hypericum pulchrum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmevatten, 250 m SV om, Boh</t>
+          <t>Billys backe, Nornäbban, Svartedalen (Kungälvs kommun), Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>326101.7579698159</v>
+        <v>326062.0975395681</v>
       </c>
       <c r="R6" t="n">
-        <v>6434647.334535607</v>
+        <v>6434700.513468524</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,7 +1235,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2016-07-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1251,17 +1245,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
+          <t>2016-07-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I dike tillsammans med bergbräken.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,22 +1265,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Gahnertz</t>
+          <t>Björn Dellming</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Gahnertz, Kåre Ström</t>
+          <t>Björn Dellming</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84693299</v>
+        <v>67640615</v>
       </c>
       <c r="B7" t="n">
-        <v>97525</v>
+        <v>95717</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,37 +1293,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>220686</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>300 m NV om gården Holmevatten, Boh</t>
+          <t>Holmevatten, 250 m SV om, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>326023</v>
+        <v>326101.7579698159</v>
       </c>
       <c r="R7" t="n">
-        <v>6435018</v>
+        <v>6434647.334535607</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,17 +1358,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>I dike tillsammans med bergbräken.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,40 +1389,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrskog, skogsväg</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Roger Gahnertz</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Gahnertz, Bertil Gilsenius</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
+          <t>Roger Gahnertz, Kåre Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120482306</v>
+        <v>84693299</v>
       </c>
       <c r="B8" t="n">
-        <v>91289</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,37 +1416,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>300 m NV om gården Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325833</v>
+        <v>326023</v>
       </c>
       <c r="R8" t="n">
-        <v>6434958</v>
+        <v>6435018</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,12 +1470,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2001-10-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2001-10-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,45 +1492,34 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog, skogsväg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Evastina Blomgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Roger Gahnertz, Bertil Gilsenius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120482283</v>
+        <v>84693301</v>
       </c>
       <c r="B9" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,37 +1527,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>221944</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>300 m NV om gården Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>326161</v>
+        <v>326023</v>
       </c>
       <c r="R9" t="n">
-        <v>6435085</v>
+        <v>6435018</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,12 +1577,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2001-10-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2001-10-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,26 +1598,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrskog, skogsväg</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Evastina Blomgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Roger Gahnertz, Bertil Gilsenius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120482301</v>
+        <v>120482306</v>
       </c>
       <c r="B10" t="n">
-        <v>84506</v>
+        <v>91289</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,41 +1635,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>241</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325958</v>
+        <v>325833</v>
       </c>
       <c r="R10" t="n">
-        <v>6434984</v>
+        <v>6434958</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1707,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1719,14 +1720,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1744,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120482269</v>
+        <v>120482283</v>
       </c>
       <c r="B11" t="n">
-        <v>5189</v>
+        <v>96312</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,21 +1756,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1784,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325947</v>
+        <v>326161</v>
       </c>
       <c r="R11" t="n">
-        <v>6434931</v>
+        <v>6435085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,21 +1826,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1861,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120482300</v>
+        <v>120482301</v>
       </c>
       <c r="B12" t="n">
-        <v>90688</v>
+        <v>84506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,21 +1858,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>241</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1904,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325883</v>
+        <v>325958</v>
       </c>
       <c r="R12" t="n">
-        <v>6434933</v>
+        <v>6434984</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,12 +1945,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Äldre granlåga.</t>
+          <t>Granstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga.</t>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1987,10 +1968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120482289</v>
+        <v>120482269</v>
       </c>
       <c r="B13" t="n">
-        <v>80550</v>
+        <v>5189</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,25 +1980,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2027,10 +2008,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325874</v>
+        <v>325947</v>
       </c>
       <c r="R13" t="n">
-        <v>6435000</v>
+        <v>6434931</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2104,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120482265</v>
+        <v>120482300</v>
       </c>
       <c r="B14" t="n">
-        <v>5189</v>
+        <v>90688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2116,38 +2097,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325912</v>
+        <v>325883</v>
       </c>
       <c r="R14" t="n">
-        <v>6434966</v>
+        <v>6434933</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,6 +2172,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2201,9 +2186,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Äldre granlåga.</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Äldre granlåga.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2221,10 +2211,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120482259</v>
+        <v>120482289</v>
       </c>
       <c r="B15" t="n">
-        <v>57363</v>
+        <v>80550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,32 +2227,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
@@ -2315,6 +2297,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2331,10 +2328,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120482292</v>
+        <v>120482265</v>
       </c>
       <c r="B16" t="n">
-        <v>80550</v>
+        <v>5189</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,25 +2340,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2371,10 +2368,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>326154</v>
+        <v>325912</v>
       </c>
       <c r="R16" t="n">
-        <v>6435071</v>
+        <v>6434966</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,10 +2445,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120482263</v>
+        <v>120482259</v>
       </c>
       <c r="B17" t="n">
-        <v>5189</v>
+        <v>57363</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2460,20 +2457,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2482,16 +2479,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325867</v>
+        <v>325874</v>
       </c>
       <c r="R17" t="n">
-        <v>6434934</v>
+        <v>6435000</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,21 +2539,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2565,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120482273</v>
+        <v>120482292</v>
       </c>
       <c r="B18" t="n">
-        <v>57363</v>
+        <v>80550</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2581,46 +2571,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325883</v>
+        <v>326154</v>
       </c>
       <c r="R18" t="n">
-        <v>6434952</v>
+        <v>6435071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2663,6 +2641,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2679,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120482255</v>
+        <v>120482263</v>
       </c>
       <c r="B19" t="n">
-        <v>57500</v>
+        <v>5189</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2691,50 +2684,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>325854</v>
+        <v>325867</v>
       </c>
       <c r="R19" t="n">
-        <v>6434976</v>
+        <v>6434934</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2777,6 +2758,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2793,10 +2789,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120482562</v>
+        <v>120482273</v>
       </c>
       <c r="B20" t="n">
-        <v>80853</v>
+        <v>57363</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2805,30 +2801,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3929</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2836,13 +2841,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>326094</v>
+        <v>325883</v>
       </c>
       <c r="R20" t="n">
-        <v>6434725</v>
+        <v>6434952</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2880,24 +2885,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2914,10 +2903,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120482298</v>
+        <v>120482255</v>
       </c>
       <c r="B21" t="n">
-        <v>96672</v>
+        <v>57500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2926,31 +2915,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2958,10 +2955,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325835</v>
+        <v>325854</v>
       </c>
       <c r="R21" t="n">
-        <v>6434955</v>
+        <v>6434976</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3002,24 +2999,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3036,10 +3017,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120482275</v>
+        <v>120482562</v>
       </c>
       <c r="B22" t="n">
-        <v>58203</v>
+        <v>80853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,37 +3033,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208249</v>
+        <v>3929</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325846</v>
+        <v>326094</v>
       </c>
       <c r="R22" t="n">
-        <v>6434961</v>
+        <v>6434725</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3120,8 +3104,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3138,10 +3138,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120482281</v>
+        <v>120482298</v>
       </c>
       <c r="B23" t="n">
-        <v>57500</v>
+        <v>96672</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,39 +3150,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>2606</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3190,10 +3182,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>325953</v>
+        <v>325835</v>
       </c>
       <c r="R23" t="n">
-        <v>6434938</v>
+        <v>6434955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3234,8 +3226,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3252,10 +3260,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120482287</v>
+        <v>120482275</v>
       </c>
       <c r="B24" t="n">
-        <v>80550</v>
+        <v>58203</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3264,25 +3272,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>208249</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3292,10 +3300,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>325854</v>
+        <v>325846</v>
       </c>
       <c r="R24" t="n">
-        <v>6434976</v>
+        <v>6434961</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3338,21 +3346,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3369,10 +3362,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120482285</v>
+        <v>120482281</v>
       </c>
       <c r="B25" t="n">
-        <v>96999</v>
+        <v>57500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3381,38 +3374,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>326004</v>
+        <v>325953</v>
       </c>
       <c r="R25" t="n">
-        <v>6434838</v>
+        <v>6434938</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,10 +3476,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120482299</v>
+        <v>120482287</v>
       </c>
       <c r="B26" t="n">
-        <v>96672</v>
+        <v>80550</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3483,42 +3488,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2606</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>325843</v>
+        <v>325854</v>
       </c>
       <c r="R26" t="n">
-        <v>6434980</v>
+        <v>6434976</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3559,23 +3560,22 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120482257</v>
+        <v>120482285</v>
       </c>
       <c r="B27" t="n">
-        <v>5169</v>
+        <v>96999</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,21 +3609,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>325867</v>
+        <v>326004</v>
       </c>
       <c r="R27" t="n">
-        <v>6434934</v>
+        <v>6434838</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3679,21 +3679,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3710,10 +3695,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120396579</v>
+        <v>120482299</v>
       </c>
       <c r="B28" t="n">
-        <v>74694</v>
+        <v>96672</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3722,38 +3707,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>2606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>325957</v>
+        <v>325843</v>
       </c>
       <c r="R28" t="n">
-        <v>6434924</v>
+        <v>6434980</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3788,43 +3777,50 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Högstubbe gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120396586</v>
+        <v>120482257</v>
       </c>
       <c r="B29" t="n">
-        <v>96677</v>
+        <v>5169</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3837,34 +3833,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2606</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>326198</v>
+        <v>325867</v>
       </c>
       <c r="R29" t="n">
-        <v>6434674</v>
+        <v>6434934</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3899,11 +3895,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Slänt till kulle</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3912,30 +3903,41 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120396573</v>
+        <v>120396579</v>
       </c>
       <c r="B30" t="n">
-        <v>96317</v>
+        <v>74694</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3944,25 +3946,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3972,10 +3974,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>325945</v>
+        <v>325957</v>
       </c>
       <c r="R30" t="n">
-        <v>6434987</v>
+        <v>6434924</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4012,7 +4014,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Vid samling av döda täd</t>
+          <t>Högstubbe gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4043,10 +4045,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120396581</v>
+        <v>120396586</v>
       </c>
       <c r="B31" t="n">
-        <v>74694</v>
+        <v>96677</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4055,25 +4057,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4083,10 +4085,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>326389</v>
+        <v>326198</v>
       </c>
       <c r="R31" t="n">
-        <v>6434623</v>
+        <v>6434674</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4123,7 +4125,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Död tall</t>
+          <t>Slänt till kulle</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4154,10 +4156,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120396575</v>
+        <v>120396573</v>
       </c>
       <c r="B32" t="n">
-        <v>74694</v>
+        <v>96317</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4166,25 +4168,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4194,10 +4196,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>325880</v>
+        <v>325945</v>
       </c>
       <c r="R32" t="n">
-        <v>6435003</v>
+        <v>6434987</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4234,7 +4236,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Torraka i brant</t>
+          <t>Vid samling av döda täd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4265,10 +4267,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120396572</v>
+        <v>120396581</v>
       </c>
       <c r="B33" t="n">
-        <v>74688</v>
+        <v>74694</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4277,25 +4279,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4305,10 +4307,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>326009</v>
+        <v>326389</v>
       </c>
       <c r="R33" t="n">
-        <v>6435073</v>
+        <v>6434623</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4345,7 +4347,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Skada på gran</t>
+          <t>Död tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4376,10 +4378,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120396578</v>
+        <v>120396575</v>
       </c>
       <c r="B34" t="n">
-        <v>94820</v>
+        <v>74694</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4388,25 +4390,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>535</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4416,10 +4418,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>325834</v>
+        <v>325880</v>
       </c>
       <c r="R34" t="n">
-        <v>6434949</v>
+        <v>6435003</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4456,7 +4458,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Torraka i brant</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4487,10 +4489,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120516634</v>
+        <v>120396572</v>
       </c>
       <c r="B35" t="n">
-        <v>57364</v>
+        <v>74688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4499,49 +4501,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>326160</v>
+        <v>326009</v>
       </c>
       <c r="R35" t="n">
-        <v>6435095</v>
+        <v>6435073</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4571,6 +4565,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Skada på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4585,22 +4584,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120516637</v>
+        <v>120396578</v>
       </c>
       <c r="B36" t="n">
-        <v>57364</v>
+        <v>94820</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4609,49 +4612,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>535</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>325879</v>
+        <v>325834</v>
       </c>
       <c r="R36" t="n">
-        <v>6434967</v>
+        <v>6434949</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4681,6 +4676,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4695,65 +4695,77 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120396577</v>
+        <v>120516634</v>
       </c>
       <c r="B37" t="n">
-        <v>94824</v>
+        <v>57364</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>535</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>325846</v>
+        <v>326160</v>
       </c>
       <c r="R37" t="n">
-        <v>6434968</v>
+        <v>6435095</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4783,11 +4795,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Brant</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4802,69 +4809,73 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120396574</v>
+        <v>120516637</v>
       </c>
       <c r="B38" t="n">
-        <v>96703</v>
+        <v>57364</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2609</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>325909</v>
+        <v>325879</v>
       </c>
       <c r="R38" t="n">
-        <v>6434968</v>
+        <v>6434967</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4894,11 +4905,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Fin, lite grövre ek</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4913,15 +4919,233 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120396577</v>
+      </c>
+      <c r="B39" t="n">
+        <v>94824</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>535</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dicranodontium denudatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>325846</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6434968</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Brant</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
           <t>Robin Karlsson</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>Robin Karlsson</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120396574</v>
+      </c>
+      <c r="B40" t="n">
+        <v>96703</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2609</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsfliksmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lejeunea cavifolia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>325909</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6434968</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fin, lite grövre ek</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
         <is>
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4169272</v>
+        <v>120482301</v>
       </c>
       <c r="B2" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>300m NV om gården Holmevatten, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>326018.8867515359</v>
+        <v>325958</v>
       </c>
       <c r="R2" t="n">
-        <v>6435013.198442956</v>
+        <v>6434984</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,38 +757,49 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4246503</v>
+        <v>120396572</v>
       </c>
       <c r="B3" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>300m NV om gården Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>326018.8867515359</v>
+        <v>326009</v>
       </c>
       <c r="R3" t="n">
-        <v>6435013.198442956</v>
+        <v>6435073</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +861,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skada på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,74 +882,68 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1053843</v>
+        <v>120396571</v>
       </c>
       <c r="B4" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3518</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nornäbban, Svartedalen, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>326282.5541622447</v>
+        <v>326175</v>
       </c>
       <c r="R4" t="n">
-        <v>6434686.656774394</v>
+        <v>6435119</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +967,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-10-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-10-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Klen björk i slänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,90 +988,68 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Elaphomyces sp</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Svedholm</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60197501</v>
+        <v>120396575</v>
       </c>
       <c r="B5" t="n">
-        <v>101222</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>837</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypericum pulchrum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nornäbban, backe, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>326084.2873558934</v>
+        <v>325880</v>
       </c>
       <c r="R5" t="n">
-        <v>6434782.816282547</v>
+        <v>6435003</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,22 +1073,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-06-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-06-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Torraka i brant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,73 +1098,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karin Magnander</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Magnander, Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>60679007</v>
+        <v>120396579</v>
       </c>
       <c r="B6" t="n">
-        <v>101222</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>837</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypericum pulchrum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Billys backe, Nornäbban, Svartedalen (Kungälvs kommun), Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>326062.0975395681</v>
+        <v>325957</v>
       </c>
       <c r="R6" t="n">
-        <v>6434700.513468524</v>
+        <v>6434924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,22 +1179,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-07-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Högstubbe gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,76 +1204,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Dellming</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67640615</v>
+        <v>120396581</v>
       </c>
       <c r="B7" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220686</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Holmevatten, 250 m SV om, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>326101.7579698159</v>
+        <v>326389</v>
       </c>
       <c r="R7" t="n">
-        <v>6434647.334535607</v>
+        <v>6434623</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,27 +1285,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-09-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I dike tillsammans med bergbräken.</t>
+          <t>Död tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,22 +1310,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Gahnertz</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Gahnertz, Kåre Ström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84693299</v>
+        <v>120396577</v>
       </c>
       <c r="B8" t="n">
-        <v>97525</v>
+        <v>96705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,37 +1337,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>535</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>300 m NV om gården Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>326023</v>
+        <v>325846</v>
       </c>
       <c r="R8" t="n">
-        <v>6435018</v>
+        <v>6434968</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,17 +1391,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>Brant</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,35 +1412,30 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrskog, skogsväg</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Gahnertz, Bertil Gilsenius</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Bohusläns Flora 2011</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84693301</v>
+        <v>120396578</v>
       </c>
       <c r="B9" t="n">
-        <v>97516</v>
+        <v>96705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,33 +1443,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221944</v>
+        <v>535</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Dicranodontium denudatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>300 m NV om gården Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>326023</v>
+        <v>325834</v>
       </c>
       <c r="R9" t="n">
-        <v>6435018</v>
+        <v>6434949</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,17 +1497,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2001-10-14</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Bohusläns flora - 2011.</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,78 +1518,79 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrskog, skogsväg</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Evastina Blomgren</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Gahnertz, Bertil Gilsenius</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Bohusläns Flora 2011</t>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120482306</v>
+        <v>60197501</v>
       </c>
       <c r="B10" t="n">
-        <v>91289</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>837</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hypericum pulchrum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Nornäbban, backe, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325833</v>
+        <v>326084</v>
       </c>
       <c r="R10" t="n">
-        <v>6434958</v>
+        <v>6434783</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1693,12 +1614,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2016-06-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2016-06-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,81 +1630,72 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Karin Magnander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Karin Magnander, Björn Dellming</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120482283</v>
+        <v>60679007</v>
       </c>
       <c r="B11" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>837</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hypericum pulchrum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Billys backe, Nornäbban, Svartedalen (Kungälvs kommun), Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>326161</v>
+        <v>326062</v>
       </c>
       <c r="R11" t="n">
-        <v>6435085</v>
+        <v>6434701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,12 +1722,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2016-07-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2016-07-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,27 +1742,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Björn Dellming</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Björn Dellming</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120482301</v>
+        <v>120482287</v>
       </c>
       <c r="B12" t="n">
-        <v>84506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,37 +1765,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>241</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325958</v>
+        <v>325854</v>
       </c>
       <c r="R12" t="n">
-        <v>6434984</v>
+        <v>6434976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,7 +1833,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1943,14 +1846,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granstubbe</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1968,37 +1866,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120482269</v>
+        <v>120482289</v>
       </c>
       <c r="B13" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2008,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325947</v>
+        <v>325874</v>
       </c>
       <c r="R13" t="n">
-        <v>6434931</v>
+        <v>6435000</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2085,15 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120482300</v>
+        <v>120482292</v>
       </c>
       <c r="B14" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,37 +1989,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325883</v>
+        <v>326154</v>
       </c>
       <c r="R14" t="n">
-        <v>6434933</v>
+        <v>6435071</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2172,7 +2057,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2186,14 +2070,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Äldre granlåga.</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2211,50 +2090,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120482289</v>
+        <v>120482300</v>
       </c>
       <c r="B15" t="n">
-        <v>80550</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325874</v>
+        <v>325883</v>
       </c>
       <c r="R15" t="n">
-        <v>6435000</v>
+        <v>6434933</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,6 +2172,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2308,9 +2186,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Äldre granlåga.</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Äldre granlåga.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2328,15 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120482265</v>
+        <v>120482306</v>
       </c>
       <c r="B16" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,21 +2222,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2368,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325912</v>
+        <v>325833</v>
       </c>
       <c r="R16" t="n">
-        <v>6434966</v>
+        <v>6434958</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2445,58 +2323,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120482259</v>
+        <v>120396573</v>
       </c>
       <c r="B17" t="n">
-        <v>57363</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325874</v>
+        <v>325945</v>
       </c>
       <c r="R17" t="n">
-        <v>6435000</v>
+        <v>6434987</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,6 +2396,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Vid samling av döda täd</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2543,49 +2413,48 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120482292</v>
+        <v>120482283</v>
       </c>
       <c r="B18" t="n">
-        <v>80550</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2595,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>326154</v>
+        <v>326161</v>
       </c>
       <c r="R18" t="n">
-        <v>6435071</v>
+        <v>6435085</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2641,21 +2510,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2672,15 +2526,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120482263</v>
+        <v>120396586</v>
       </c>
       <c r="B19" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,34 +2537,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>325867</v>
+        <v>326198</v>
       </c>
       <c r="R19" t="n">
-        <v>6434934</v>
+        <v>6434674</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2750,6 +2599,11 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Slänt till kulle</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2758,82 +2612,58 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120482273</v>
+        <v>120482298</v>
       </c>
       <c r="B20" t="n">
-        <v>57363</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2841,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>325883</v>
+        <v>325835</v>
       </c>
       <c r="R20" t="n">
-        <v>6434952</v>
+        <v>6434955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2885,8 +2715,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2903,51 +2749,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120482255</v>
+        <v>120482299</v>
       </c>
       <c r="B21" t="n">
-        <v>57500</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2955,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325854</v>
+        <v>325843</v>
       </c>
       <c r="R21" t="n">
-        <v>6434976</v>
+        <v>6434980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2999,8 +2832,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3017,15 +2866,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120482562</v>
+        <v>120396574</v>
       </c>
       <c r="B22" t="n">
-        <v>80853</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,40 +2877,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3929</v>
+        <v>2609</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Kring Holmevatten i Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>326094</v>
+        <v>325909</v>
       </c>
       <c r="R22" t="n">
-        <v>6434725</v>
+        <v>6434968</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3098,55 +2939,43 @@
           <t>2024-10-06</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fin, lite grövre ek</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>hassel</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Corylus avellana</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120482298</v>
+        <v>1053843</v>
       </c>
       <c r="B23" t="n">
-        <v>96672</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3154,41 +2983,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>3518</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Nornäbban, Svartedalen, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>325835</v>
+        <v>326283</v>
       </c>
       <c r="R23" t="n">
-        <v>6434955</v>
+        <v>6434687</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3212,12 +3037,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2011-10-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2011-10-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,49 +3051,38 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>granskog</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Elaphomyces sp</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Johan Svedholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Johan Svedholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120482275</v>
+        <v>120482562</v>
       </c>
       <c r="B24" t="n">
-        <v>58203</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81655</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,37 +3090,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208249</v>
+        <v>3929</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Läderskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Encoelia furfuracea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Roth.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>325846</v>
+        <v>326094</v>
       </c>
       <c r="R24" t="n">
-        <v>6434961</v>
+        <v>6434725</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3344,8 +3161,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3362,49 +3195,40 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120482281</v>
+        <v>120482259</v>
       </c>
       <c r="B25" t="n">
-        <v>57500</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3414,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>325953</v>
+        <v>325874</v>
       </c>
       <c r="R25" t="n">
-        <v>6434938</v>
+        <v>6435000</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3476,50 +3300,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120482287</v>
+        <v>120482273</v>
       </c>
       <c r="B26" t="n">
-        <v>80550</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>325854</v>
+        <v>325883</v>
       </c>
       <c r="R26" t="n">
-        <v>6434976</v>
+        <v>6434952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3562,21 +3393,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3593,15 +3409,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120482285</v>
+        <v>120516629</v>
       </c>
       <c r="B27" t="n">
-        <v>96999</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,37 +3420,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>326004</v>
+        <v>326186</v>
       </c>
       <c r="R27" t="n">
-        <v>6434838</v>
+        <v>6435083</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3695,15 +3518,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120482299</v>
+        <v>120516634</v>
       </c>
       <c r="B28" t="n">
-        <v>96672</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3711,27 +3529,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3739,13 +3561,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>325843</v>
+        <v>326160</v>
       </c>
       <c r="R28" t="n">
-        <v>6434980</v>
+        <v>6435095</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3783,24 +3605,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3817,15 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120482257</v>
+        <v>120516637</v>
       </c>
       <c r="B29" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3833,37 +3634,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>325867</v>
+        <v>325879</v>
       </c>
       <c r="R29" t="n">
-        <v>6434934</v>
+        <v>6434967</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3903,21 +3712,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3934,50 +3728,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120396579</v>
+        <v>120482257</v>
       </c>
       <c r="B30" t="n">
-        <v>74694</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>325957</v>
+        <v>325867</v>
       </c>
       <c r="R30" t="n">
-        <v>6434924</v>
+        <v>6434934</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4012,11 +3801,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Högstubbe gran</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4025,70 +3809,88 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120396586</v>
+        <v>120482255</v>
       </c>
       <c r="B31" t="n">
-        <v>96677</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>326198</v>
+        <v>325854</v>
       </c>
       <c r="R31" t="n">
-        <v>6434674</v>
+        <v>6434976</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4123,11 +3925,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Slänt till kulle</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4140,66 +3937,69 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120396573</v>
+        <v>120482281</v>
       </c>
       <c r="B32" t="n">
-        <v>96317</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>325945</v>
+        <v>325953</v>
       </c>
       <c r="R32" t="n">
-        <v>6434987</v>
+        <v>6434938</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4234,11 +4034,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Vid samling av döda täd</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4251,66 +4046,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120396581</v>
+        <v>120482263</v>
       </c>
       <c r="B33" t="n">
-        <v>74694</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>326389</v>
+        <v>325867</v>
       </c>
       <c r="R33" t="n">
-        <v>6434623</v>
+        <v>6434934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4345,11 +4131,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Död tall</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4358,70 +4139,76 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120396575</v>
+        <v>120482265</v>
       </c>
       <c r="B34" t="n">
-        <v>74694</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>325880</v>
+        <v>325912</v>
       </c>
       <c r="R34" t="n">
-        <v>6435003</v>
+        <v>6434966</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4456,11 +4243,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Torraka i brant</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4469,35 +4251,41 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120396572</v>
+        <v>120482269</v>
       </c>
       <c r="B35" t="n">
-        <v>74688</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4505,34 +4293,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>306</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>326009</v>
+        <v>325947</v>
       </c>
       <c r="R35" t="n">
-        <v>6435073</v>
+        <v>6434931</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4567,11 +4355,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Skada på gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4580,35 +4363,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120396578</v>
+        <v>120482275</v>
       </c>
       <c r="B36" t="n">
-        <v>94820</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4616,34 +4405,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>535</v>
+        <v>208249</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>325834</v>
+        <v>325846</v>
       </c>
       <c r="R36" t="n">
-        <v>6434949</v>
+        <v>6434961</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4678,11 +4467,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4695,77 +4479,71 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
-        </is>
-      </c>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120516634</v>
+        <v>67640615</v>
       </c>
       <c r="B37" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>Holmevatten, 250 m SV om, Boh</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>326160</v>
+        <v>326102</v>
       </c>
       <c r="R37" t="n">
-        <v>6435095</v>
+        <v>6434647</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4789,12 +4567,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2017-09-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2017-09-21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I dike tillsammans med bergbräken.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4809,73 +4592,56 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Gahnertz</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Roger Gahnertz, Kåre Ström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120516637</v>
+        <v>4169272</v>
       </c>
       <c r="B38" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Holmevatten, Boh</t>
+          <t>300m NV om gården Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>325879</v>
+        <v>326019</v>
       </c>
       <c r="R38" t="n">
-        <v>6434967</v>
+        <v>6435013</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4899,12 +4665,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2001-10-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2001-10-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4915,31 +4681,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Föreningen Bohusläns Flora</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120396577</v>
+        <v>84693301</v>
       </c>
       <c r="B39" t="n">
-        <v>94824</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,37 +4713,33 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>535</v>
+        <v>221944</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Brid.) E.Britton</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>300 m NV om gården Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>325846</v>
+        <v>326023</v>
       </c>
       <c r="R39" t="n">
-        <v>6434968</v>
+        <v>6435018</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5001,17 +4763,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2001-10-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2001-10-14</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Brant</t>
+          <t>Bohusläns flora - 2011.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5022,35 +4784,35 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrskog, skogsväg</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Evastina Blomgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Roger Gahnertz, Bertil Gilsenius</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Bohusläns Flora 2011</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120396574</v>
+        <v>120482285</v>
       </c>
       <c r="B40" t="n">
-        <v>96703</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5058,34 +4820,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2609</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kring Holmevatten i Svartedalen, Boh</t>
+          <t>Holmevatten, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>325909</v>
+        <v>326004</v>
       </c>
       <c r="R40" t="n">
-        <v>6434968</v>
+        <v>6434838</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5120,11 +4882,6 @@
           <t>2024-10-06</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Fin, lite grövre ek</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5137,17 +4894,226 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4246503</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>300m NV om gården Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>326019</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6435013</v>
+      </c>
+      <c r="S41" t="n">
+        <v>50</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2001-10-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2001-10-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>84693299</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>300 m NV om gården Holmevatten, Boh</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>326023</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6435018</v>
+      </c>
+      <c r="S42" t="n">
+        <v>100</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Romelanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2001-10-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2001-10-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Barrskog, skogsväg</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Evastina Blomgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Roger Gahnertz, Bertil Gilsenius</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396572</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396571</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396575</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396579</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396581</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396577</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1535,6 +1575,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396578</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60197501</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60679007</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482287</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,6 +2035,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482289</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2152,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482292</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482300</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2320,6 +2395,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482306</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2426,6 +2506,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396573</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2523,6 +2608,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482283</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2627,6 +2717,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396586</t>
         </is>
       </c>
     </row>
@@ -2746,6 +2841,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482298</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2863,6 +2963,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482299</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2969,6 +3074,11 @@
           <t>Skogsgruppen: Inventering av avverkningsanmält område A 38982-2024</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120396574</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3076,6 +3186,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1053843</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3192,6 +3307,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482562</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3297,6 +3417,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482259</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3406,6 +3531,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482273</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3515,6 +3645,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516629</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3620,6 +3755,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516634</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3725,6 +3865,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120516637</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3837,6 +3982,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482257</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3946,6 +4096,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482255</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4055,6 +4210,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482281</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4167,6 +4327,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482263</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4279,6 +4444,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482265</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4391,6 +4561,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482269</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4488,6 +4663,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482275</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4601,6 +4781,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67640615</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4699,6 +4884,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4169272</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4806,6 +4996,11 @@
           <t>Bohusläns Flora 2011</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84693301</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4903,6 +5098,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120482285</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5005,6 +5205,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4246503</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5116,8 +5321,56 @@
           <t>Bohusläns Flora 2011</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84693299</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>